--- a/assessment/templates/records-manager-checklist.xlsx
+++ b/assessment/templates/records-manager-checklist.xlsx
@@ -832,7 +832,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Frontier preview enrollment record for tenant and admin accounts; Cowork availability configuration (scoped group or blocked) with approval; Approved Cowork plugin inventory and connector authentication records; Deployment/pinning approvals and supervision/audit coverage evidence</t>
+          <t>Usage-based billing scope export (user/group assignments) with approver; Discovery-setting decision record and access-request workflow evidence; Model-policy record for Anthropic family and Claude Fable 5 (Preview); Cowork Browsing tenant-toggle decision tied to browser-control review; Consumption-limit policy and recent spend/consumption report; Approved plugin, uploaded package, and custom-skill inventory with owner; Purview coverage evidence (audit/eDiscovery/DLP alignment) and gap log</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr"/>

--- a/assessment/templates/records-manager-checklist.xlsx
+++ b/assessment/templates/records-manager-checklist.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration for Copilot records (if applicable); Retrievability test results for examiner response readiness; Retention duration aligned to SEC 17a-4 / FINRA 4511</t>
+          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration or audit-trail alternative documentation per Rule 17a-4(f)(2) (SEC Release No. 34-96034, 87 FR 66412 (Nov. 3, 2022)) for Copilot records; Retrievability test results for examiner response readiness; Retention duration aligned to Rule 17a-4(f)(2) / FINRA 4511</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>

--- a/assessment/templates/records-manager-checklist.xlsx
+++ b/assessment/templates/records-manager-checklist.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration or audit-trail alternative documentation per Rule 17a-4(f)(2) (SEC Release No. 34-96034, 87 FR 66412 (Nov. 3, 2022)) for Copilot records; Retrievability test results for examiner response readiness; Retention duration aligned to Rule 17a-4(f)(2) / FINRA 4511</t>
+          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration or audit-trail alternative documentation per Rule 17a-4(f)(2) (SEC Release No. 34-96034, 87 FR 66412 (Nov. 3, 2022)) for Copilot records; Retrievability test results for examiner response readiness; Retention duration aligned to SEC Rule 17a-4 / FINRA 4511</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>

--- a/assessment/templates/records-manager-checklist.xlsx
+++ b/assessment/templates/records-manager-checklist.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration for Copilot records (if applicable); Retrievability test results for examiner response readiness; Retention duration aligned to SEC 17a-4 / FINRA 4511</t>
+          <t>Books-and-records policy covering Copilot interactions; WORM archive configuration or audit-trail alternative documentation per Rule 17a-4(f)(2) (SEC Release No. 34-96034, 87 FR 66412 (Nov. 3, 2022)) for Copilot records; Retrievability test results for examiner response readiness; Retention duration aligned to SEC Rule 17a-4 / FINRA 4511</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>

--- a/assessment/templates/records-manager-checklist.xlsx
+++ b/assessment/templates/records-manager-checklist.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>eDiscovery for Copilot-Generated Content</t>
+          <t>Are eDiscovery cases and holds configured to capture Copilot interaction content when legally required?</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
